--- a/Cursor/3_쿠팡 모니터링/cp_payment.xlsx
+++ b/Cursor/3_쿠팡 모니터링/cp_payment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Cursor/coupang-monitoring-vercel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\hana\Cursor\3_쿠팡 모니터링\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AAEFE6-93A9-6C41-AAA1-DBCAFFEF3144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{331BE418-4C4F-4B4A-9B35-94BEDA8862CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주요지표" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2686,10 +2689,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="42" formatCode="_(&quot;₩&quot;* #,##0_);_(&quot;₩&quot;* \(#,##0\);_(&quot;₩&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="#,##0.0"/>
+    <numFmt numFmtId="176" formatCode="_(&quot;₩&quot;* #,##0_);_(&quot;₩&quot;* \(#,##0\);_(&quot;₩&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -2961,7 +2964,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2984,16 +2987,16 @@
     <xf numFmtId="3" fontId="7" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3011,16 +3014,16 @@
     <xf numFmtId="3" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -3070,9 +3073,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3110,7 +3113,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3216,7 +3219,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3358,7 +3361,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3367,15 +3370,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R271"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="22" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="15" width="15.83203125" customWidth="1"/>
+    <col min="1" max="15" width="15.796875" customWidth="1"/>
     <col min="16" max="16" width="11" style="18" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.1640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.19921875" style="18" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.69921875" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17">
+    <row r="1" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -3399,7 +3402,7 @@
       <c r="Q1" s="26"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" ht="17">
+    <row r="2" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
@@ -3413,7 +3416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17">
+    <row r="3" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
@@ -3437,7 +3440,7 @@
       <c r="Q3" s="25"/>
       <c r="R3" s="25"/>
     </row>
-    <row r="4" spans="1:18" ht="17">
+    <row r="4" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="21"/>
       <c r="B4" s="22" t="s">
         <v>2</v>
@@ -3461,7 +3464,7 @@
       <c r="Q4" s="23"/>
       <c r="R4" s="23"/>
     </row>
-    <row r="5" spans="1:18" ht="17">
+    <row r="5" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="21"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3515,7 +3518,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17">
+    <row r="6" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>790</v>
       </c>
@@ -3574,7 +3577,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17">
+    <row r="7" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>791</v>
       </c>
@@ -3633,7 +3636,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17">
+    <row r="8" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
         <v>792</v>
       </c>
@@ -3692,7 +3695,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17">
+    <row r="9" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
         <v>794</v>
       </c>
@@ -3751,7 +3754,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17">
+    <row r="10" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A10" s="12" t="s">
         <v>798</v>
       </c>
@@ -3810,7 +3813,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17">
+    <row r="11" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A11" s="12" t="s">
         <v>800</v>
       </c>
@@ -3869,7 +3872,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17">
+    <row r="12" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="12" t="s">
         <v>802</v>
       </c>
@@ -3928,7 +3931,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17">
+    <row r="13" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="12" t="s">
         <v>803</v>
       </c>
@@ -3987,7 +3990,7 @@
         <v>-4.9576136731741362E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17">
+    <row r="14" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="12" t="s">
         <v>805</v>
       </c>
@@ -4046,7 +4049,7 @@
         <v>-4.8931555672281732E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17">
+    <row r="15" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="12" t="s">
         <v>806</v>
       </c>
@@ -4105,7 +4108,7 @@
         <v>-1.4378684476480058E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17">
+    <row r="16" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="12" t="s">
         <v>807</v>
       </c>
@@ -4164,7 +4167,7 @@
         <v>-1.4381173736199885E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17">
+    <row r="17" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
         <v>810</v>
       </c>
@@ -4223,7 +4226,7 @@
         <v>-2.9181971093327996E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17">
+    <row r="18" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A18" s="12" t="s">
         <v>811</v>
       </c>
@@ -4282,7 +4285,7 @@
         <v>-4.2866046015887192E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17">
+    <row r="19" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A19" s="12" t="s">
         <v>812</v>
       </c>
@@ -4341,7 +4344,7 @@
         <v>-5.8386489959590643E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17">
+    <row r="20" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="12" t="s">
         <v>735</v>
       </c>
@@ -4400,7 +4403,7 @@
         <v>-8.8265021631567325E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17">
+    <row r="21" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
         <v>737</v>
       </c>
@@ -4459,7 +4462,7 @@
         <v>-7.1461003428372152E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17">
+    <row r="22" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A22" s="12" t="s">
         <v>739</v>
       </c>
@@ -4518,7 +4521,7 @@
         <v>-0.10334655809467724</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17">
+    <row r="23" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A23" s="12" t="s">
         <v>741</v>
       </c>
@@ -4577,7 +4580,7 @@
         <v>-6.3275783993910401E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17">
+    <row r="24" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A24" s="12" t="s">
         <v>743</v>
       </c>
@@ -4636,7 +4639,7 @@
         <v>-1.5429861784374364E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17">
+    <row r="25" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A25" s="12" t="s">
         <v>745</v>
       </c>
@@ -4695,7 +4698,7 @@
         <v>-5.3617072023426993E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17">
+    <row r="26" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A26" s="12" t="s">
         <v>746</v>
       </c>
@@ -4754,7 +4757,7 @@
         <v>-1.3176864349319816E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17">
+    <row r="27" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A27" s="12" t="s">
         <v>750</v>
       </c>
@@ -4813,7 +4816,7 @@
         <v>1.6931459433652613E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17">
+    <row r="28" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A28" s="12" t="s">
         <v>752</v>
       </c>
@@ -4872,7 +4875,7 @@
         <v>2.1705566381000428E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17">
+    <row r="29" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A29" s="12" t="s">
         <v>753</v>
       </c>
@@ -4931,7 +4934,7 @@
         <v>3.8965932699587452E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17">
+    <row r="30" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A30" s="12" t="s">
         <v>756</v>
       </c>
@@ -4990,7 +4993,7 @@
         <v>7.0268649164544172E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17">
+    <row r="31" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A31" s="12" t="s">
         <v>758</v>
       </c>
@@ -5049,7 +5052,7 @@
         <v>9.2244270980281519E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="17">
+    <row r="32" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A32" s="12" t="s">
         <v>760</v>
       </c>
@@ -5108,7 +5111,7 @@
         <v>7.9638856834700485E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="17">
+    <row r="33" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A33" s="12" t="s">
         <v>762</v>
       </c>
@@ -5167,7 +5170,7 @@
         <v>-3.8936060855501047E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="17">
+    <row r="34" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A34" s="12" t="s">
         <v>763</v>
       </c>
@@ -5226,7 +5229,7 @@
         <v>-2.4173642910076471E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="17">
+    <row r="35" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A35" s="12" t="s">
         <v>765</v>
       </c>
@@ -5285,7 +5288,7 @@
         <v>-8.2380674495052333E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="17">
+    <row r="36" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A36" s="12" t="s">
         <v>766</v>
       </c>
@@ -5344,7 +5347,7 @@
         <v>-4.4567506471855013E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="17">
+    <row r="37" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A37" s="12" t="s">
         <v>769</v>
       </c>
@@ -5403,7 +5406,7 @@
         <v>-4.594642312646964E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="17">
+    <row r="38" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A38" s="12" t="s">
         <v>770</v>
       </c>
@@ -5462,7 +5465,7 @@
         <v>-1.2064141662349362E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="17">
+    <row r="39" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A39" s="12" t="s">
         <v>772</v>
       </c>
@@ -5521,7 +5524,7 @@
         <v>-3.2279586026449196E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="17">
+    <row r="40" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A40" s="12" t="s">
         <v>773</v>
       </c>
@@ -5580,7 +5583,7 @@
         <v>-2.7973715965339346E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="17">
+    <row r="41" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A41" s="12" t="s">
         <v>774</v>
       </c>
@@ -5639,7 +5642,7 @@
         <v>8.7321075988099311E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="17">
+    <row r="42" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A42" s="12" t="s">
         <v>776</v>
       </c>
@@ -5698,7 +5701,7 @@
         <v>5.1708462232755312E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="17">
+    <row r="43" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A43" s="12" t="s">
         <v>777</v>
       </c>
@@ -5757,7 +5760,7 @@
         <v>1.4767446202098399E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="17">
+    <row r="44" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A44" s="12" t="s">
         <v>778</v>
       </c>
@@ -5816,7 +5819,7 @@
         <v>-3.0311445950278619E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="17">
+    <row r="45" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A45" s="12" t="s">
         <v>781</v>
       </c>
@@ -5875,7 +5878,7 @@
         <v>-4.0160914280580939E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="17">
+    <row r="46" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A46" s="12" t="s">
         <v>783</v>
       </c>
@@ -5934,7 +5937,7 @@
         <v>1.5026407632160585E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="17">
+    <row r="47" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A47" s="12" t="s">
         <v>785</v>
       </c>
@@ -5993,7 +5996,7 @@
         <v>2.0592009518271358E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="17">
+    <row r="48" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A48" s="12" t="s">
         <v>787</v>
       </c>
@@ -6052,7 +6055,7 @@
         <v>-2.0559511351690173E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="17">
+    <row r="49" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A49" s="12" t="s">
         <v>788</v>
       </c>
@@ -6111,7 +6114,7 @@
         <v>-4.3312426408462279E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="17">
+    <row r="50" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A50" s="12" t="s">
         <v>789</v>
       </c>
@@ -6170,7 +6173,7 @@
         <v>-8.433660168235102E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="17">
+    <row r="51" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A51" s="12" t="s">
         <v>671</v>
       </c>
@@ -6229,7 +6232,7 @@
         <v>-9.997549652265289E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="17">
+    <row r="52" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A52" s="12" t="s">
         <v>675</v>
       </c>
@@ -6288,7 +6291,7 @@
         <v>-3.4605739662588188E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="17">
+    <row r="53" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A53" s="12" t="s">
         <v>678</v>
       </c>
@@ -6347,7 +6350,7 @@
         <v>-1.8781473224341528E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="17">
+    <row r="54" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A54" s="12" t="s">
         <v>679</v>
       </c>
@@ -6406,7 +6409,7 @@
         <v>-3.3639890691314907E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="17">
+    <row r="55" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A55" s="12" t="s">
         <v>682</v>
       </c>
@@ -6465,7 +6468,7 @@
         <v>-3.4155714131469685E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="17">
+    <row r="56" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A56" s="12" t="s">
         <v>683</v>
       </c>
@@ -6524,7 +6527,7 @@
         <v>3.0286296037125269E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="17">
+    <row r="57" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A57" s="12" t="s">
         <v>684</v>
       </c>
@@ -6583,7 +6586,7 @@
         <v>7.2901416419514989E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="17">
+    <row r="58" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A58" s="12" t="s">
         <v>686</v>
       </c>
@@ -6642,7 +6645,7 @@
         <v>7.8249596491886356E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="17">
+    <row r="59" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A59" s="12" t="s">
         <v>688</v>
       </c>
@@ -6701,7 +6704,7 @@
         <v>-1.8234038319420859E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="17">
+    <row r="60" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A60" s="12" t="s">
         <v>690</v>
       </c>
@@ -6760,7 +6763,7 @@
         <v>-1.2615536737715089E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="17">
+    <row r="61" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A61" s="12" t="s">
         <v>692</v>
       </c>
@@ -6819,7 +6822,7 @@
         <v>9.3879431367735518E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="17">
+    <row r="62" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A62" s="12" t="s">
         <v>694</v>
       </c>
@@ -6878,7 +6881,7 @@
         <v>1.1363029182459253E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="17">
+    <row r="63" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A63" s="12" t="s">
         <v>695</v>
       </c>
@@ -6937,7 +6940,7 @@
         <v>-2.0010160902201805E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="17">
+    <row r="64" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A64" s="12" t="s">
         <v>696</v>
       </c>
@@ -6996,7 +6999,7 @@
         <v>-1.0883661748307238E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="17">
+    <row r="65" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A65" s="12" t="s">
         <v>698</v>
       </c>
@@ -7055,7 +7058,7 @@
         <v>-1.3500160372571516E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="17">
+    <row r="66" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A66" s="12" t="s">
         <v>700</v>
       </c>
@@ -7114,7 +7117,7 @@
         <v>-3.0532482184527577E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="17">
+    <row r="67" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A67" s="12" t="s">
         <v>701</v>
       </c>
@@ -7173,7 +7176,7 @@
         <v>-1.3147295929838748E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="17">
+    <row r="68" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A68" s="12" t="s">
         <v>705</v>
       </c>
@@ -7232,7 +7235,7 @@
         <v>0.14378102190481998</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="17">
+    <row r="69" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A69" s="12" t="s">
         <v>707</v>
       </c>
@@ -7291,7 +7294,7 @@
         <v>9.7194835940788663E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="17">
+    <row r="70" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A70" s="12" t="s">
         <v>710</v>
       </c>
@@ -7350,7 +7353,7 @@
         <v>9.7135711370859815E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="17">
+    <row r="71" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A71" s="12" t="s">
         <v>712</v>
       </c>
@@ -7409,7 +7412,7 @@
         <v>7.4028027934533322E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="17">
+    <row r="72" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A72" s="12" t="s">
         <v>713</v>
       </c>
@@ -7468,7 +7471,7 @@
         <v>9.2005409975750269E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="17">
+    <row r="73" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A73" s="12" t="s">
         <v>714</v>
       </c>
@@ -7527,7 +7530,7 @@
         <v>0.1117249477411439</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="17">
+    <row r="74" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A74" s="12" t="s">
         <v>715</v>
       </c>
@@ -7586,7 +7589,7 @@
         <v>7.1222295280048059E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="17">
+    <row r="75" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A75" s="12" t="s">
         <v>719</v>
       </c>
@@ -7645,7 +7648,7 @@
         <v>-7.8816912985699858E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="17">
+    <row r="76" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A76" s="12" t="s">
         <v>723</v>
       </c>
@@ -7704,7 +7707,7 @@
         <v>-5.6260742563250483E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="17">
+    <row r="77" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A77" s="12" t="s">
         <v>725</v>
       </c>
@@ -7763,7 +7766,7 @@
         <v>-5.8508578567196606E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="17">
+    <row r="78" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A78" s="12" t="s">
         <v>727</v>
       </c>
@@ -7822,7 +7825,7 @@
         <v>-4.4088129251221011E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="17">
+    <row r="79" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A79" s="12" t="s">
         <v>728</v>
       </c>
@@ -7881,7 +7884,7 @@
         <v>-5.2544105822421808E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="17">
+    <row r="80" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A80" s="12" t="s">
         <v>732</v>
       </c>
@@ -7940,7 +7943,7 @@
         <v>-1.672309263492722E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="17">
+    <row r="81" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A81" s="12" t="s">
         <v>734</v>
       </c>
@@ -7999,7 +8002,7 @@
         <v>-2.0180261168792894E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17">
+    <row r="82" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A82" s="12" t="s">
         <v>584</v>
       </c>
@@ -8058,7 +8061,7 @@
         <v>-8.1146810512444881E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="17">
+    <row r="83" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A83" s="12" t="s">
         <v>589</v>
       </c>
@@ -8117,7 +8120,7 @@
         <v>7.3721021165696898E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="17">
+    <row r="84" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A84" s="12" t="s">
         <v>591</v>
       </c>
@@ -8176,7 +8179,7 @@
         <v>-3.0369032757696E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="17">
+    <row r="85" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A85" s="12" t="s">
         <v>593</v>
       </c>
@@ -8235,7 +8238,7 @@
         <v>-2.7407149646049414E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="17">
+    <row r="86" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A86" s="12" t="s">
         <v>594</v>
       </c>
@@ -8294,7 +8297,7 @@
         <v>-1.6616554526908509E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="17">
+    <row r="87" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A87" s="12" t="s">
         <v>595</v>
       </c>
@@ -8353,7 +8356,7 @@
         <v>1.7111318350069477E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="17">
+    <row r="88" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A88" s="12" t="s">
         <v>596</v>
       </c>
@@ -8412,7 +8415,7 @@
         <v>2.5069731309953238E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="17">
+    <row r="89" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A89" s="12" t="s">
         <v>601</v>
       </c>
@@ -8471,7 +8474,7 @@
         <v>5.2899429516857083E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="17">
+    <row r="90" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A90" s="12" t="s">
         <v>606</v>
       </c>
@@ -8530,7 +8533,7 @@
         <v>9.7250149670375062E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="17">
+    <row r="91" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A91" s="12" t="s">
         <v>610</v>
       </c>
@@ -8589,7 +8592,7 @@
         <v>1.4051492883881132E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="17">
+    <row r="92" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A92" s="12" t="s">
         <v>614</v>
       </c>
@@ -8648,7 +8651,7 @@
         <v>5.3208304853041698E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="17">
+    <row r="93" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A93" s="12" t="s">
         <v>615</v>
       </c>
@@ -8707,7 +8710,7 @@
         <v>1.3646012099069838E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="17">
+    <row r="94" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A94" s="12" t="s">
         <v>617</v>
       </c>
@@ -8766,7 +8769,7 @@
         <v>-4.2839607042440241E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="17">
+    <row r="95" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A95" s="12" t="s">
         <v>619</v>
       </c>
@@ -8825,7 +8828,7 @@
         <v>-1.5157536205726421E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="17">
+    <row r="96" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A96" s="12" t="s">
         <v>620</v>
       </c>
@@ -8884,7 +8887,7 @@
         <v>6.2997657223348061E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="17">
+    <row r="97" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A97" s="12" t="s">
         <v>626</v>
       </c>
@@ -8943,7 +8946,7 @@
         <v>9.4077526518805354E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="17">
+    <row r="98" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A98" s="12" t="s">
         <v>629</v>
       </c>
@@ -9002,7 +9005,7 @@
         <v>1.3626285126639274E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="17">
+    <row r="99" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A99" s="12" t="s">
         <v>630</v>
       </c>
@@ -9061,7 +9064,7 @@
         <v>-0.12797187196359727</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="17">
+    <row r="100" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A100" s="12" t="s">
         <v>635</v>
       </c>
@@ -9120,7 +9123,7 @@
         <v>-0.13602719180104264</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="17">
+    <row r="101" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A101" s="12" t="s">
         <v>638</v>
       </c>
@@ -9179,7 +9182,7 @@
         <v>-0.11876103958720637</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="17">
+    <row r="102" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A102" s="12" t="s">
         <v>643</v>
       </c>
@@ -9238,7 +9241,7 @@
         <v>-0.28211936428288376</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="17">
+    <row r="103" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A103" s="12" t="s">
         <v>646</v>
       </c>
@@ -9297,7 +9300,7 @@
         <v>-0.41027740073375607</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="17">
+    <row r="104" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A104" s="12" t="s">
         <v>648</v>
       </c>
@@ -9356,7 +9359,7 @@
         <v>-0.36259483278076715</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="17">
+    <row r="105" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A105" s="12" t="s">
         <v>650</v>
       </c>
@@ -9415,7 +9418,7 @@
         <v>-0.24575010558708144</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="17">
+    <row r="106" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A106" s="12" t="s">
         <v>653</v>
       </c>
@@ -9474,7 +9477,7 @@
         <v>-4.4246915224708645E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="17">
+    <row r="107" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A107" s="12" t="s">
         <v>657</v>
       </c>
@@ -9533,7 +9536,7 @@
         <v>0.19275243321359578</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="17">
+    <row r="108" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A108" s="12" t="s">
         <v>661</v>
       </c>
@@ -9592,7 +9595,7 @@
         <v>0.19501003831856026</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="17">
+    <row r="109" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A109" s="12" t="s">
         <v>665</v>
       </c>
@@ -9651,7 +9654,7 @@
         <v>0.40663066772463946</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="17">
+    <row r="110" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A110" s="12" t="s">
         <v>666</v>
       </c>
@@ -9710,7 +9713,7 @@
         <v>0.60432808083400347</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="17">
+    <row r="111" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A111" s="12" t="s">
         <v>670</v>
       </c>
@@ -9769,7 +9772,7 @@
         <v>0.42043938079116122</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="17">
+    <row r="112" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A112" s="12" t="s">
         <v>503</v>
       </c>
@@ -9828,7 +9831,7 @@
         <v>0.29850038037479659</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="17">
+    <row r="113" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A113" s="12" t="s">
         <v>506</v>
       </c>
@@ -9887,7 +9890,7 @@
         <v>0.16221080793346837</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="17">
+    <row r="114" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A114" s="12" t="s">
         <v>507</v>
       </c>
@@ -9946,7 +9949,7 @@
         <v>-6.9731360021291419E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="17">
+    <row r="115" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A115" s="12" t="s">
         <v>510</v>
       </c>
@@ -10005,7 +10008,7 @@
         <v>-6.2908470880925507E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="17">
+    <row r="116" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A116" s="12" t="s">
         <v>515</v>
       </c>
@@ -10064,7 +10067,7 @@
         <v>-4.3109297054079516E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="17">
+    <row r="117" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A117" s="12" t="s">
         <v>518</v>
       </c>
@@ -10123,7 +10126,7 @@
         <v>-9.2803992550777141E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="17">
+    <row r="118" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A118" s="12" t="s">
         <v>522</v>
       </c>
@@ -10182,7 +10185,7 @@
         <v>-1.5934947814597724E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="17">
+    <row r="119" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A119" s="12" t="s">
         <v>526</v>
       </c>
@@ -10241,7 +10244,7 @@
         <v>-4.1911287438082021E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="17">
+    <row r="120" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A120" s="12" t="s">
         <v>527</v>
       </c>
@@ -10300,7 +10303,7 @@
         <v>-6.250065430513746E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="17">
+    <row r="121" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A121" s="12" t="s">
         <v>528</v>
       </c>
@@ -10359,7 +10362,7 @@
         <v>-1.713076765217492E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="17">
+    <row r="122" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A122" s="12" t="s">
         <v>531</v>
       </c>
@@ -10418,7 +10421,7 @@
         <v>-1.1026771374260747E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="17">
+    <row r="123" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A123" s="12" t="s">
         <v>533</v>
       </c>
@@ -10477,7 +10480,7 @@
         <v>9.8902857085815168E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="17">
+    <row r="124" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A124" s="12" t="s">
         <v>536</v>
       </c>
@@ -10536,7 +10539,7 @@
         <v>1.5748988624940456E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="17">
+    <row r="125" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A125" s="12" t="s">
         <v>541</v>
       </c>
@@ -10595,7 +10598,7 @@
         <v>-7.9568187142934378E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="17">
+    <row r="126" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A126" s="12" t="s">
         <v>543</v>
       </c>
@@ -10654,7 +10657,7 @@
         <v>-7.5179965875899341E-3</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="17">
+    <row r="127" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A127" s="12" t="s">
         <v>545</v>
       </c>
@@ -10713,7 +10716,7 @@
         <v>3.048286832852568E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="17">
+    <row r="128" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A128" s="12" t="s">
         <v>546</v>
       </c>
@@ -10772,7 +10775,7 @@
         <v>-4.5096837292603033E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="17">
+    <row r="129" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A129" s="12" t="s">
         <v>551</v>
       </c>
@@ -10831,7 +10834,7 @@
         <v>0.15178518677519789</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="17">
+    <row r="130" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A130" s="12" t="s">
         <v>553</v>
       </c>
@@ -10890,7 +10893,7 @@
         <v>0.11712682607388451</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="17">
+    <row r="131" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A131" s="12" t="s">
         <v>556</v>
       </c>
@@ -10949,7 +10952,7 @@
         <v>8.4280443937562621E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="17">
+    <row r="132" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A132" s="12" t="s">
         <v>560</v>
       </c>
@@ -11008,7 +11011,7 @@
         <v>9.4479495192732896E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="17">
+    <row r="133" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A133" s="12" t="s">
         <v>563</v>
       </c>
@@ -11067,7 +11070,7 @@
         <v>0.11906701391961018</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="17">
+    <row r="134" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A134" s="12" t="s">
         <v>564</v>
       </c>
@@ -11126,7 +11129,7 @@
         <v>0.11429874120028126</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="17">
+    <row r="135" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A135" s="12" t="s">
         <v>566</v>
       </c>
@@ -11185,7 +11188,7 @@
         <v>0.13295609082450224</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="17">
+    <row r="136" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A136" s="12" t="s">
         <v>567</v>
       </c>
@@ -11244,7 +11247,7 @@
         <v>-5.2333588606976629E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="17">
+    <row r="137" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A137" s="12" t="s">
         <v>569</v>
       </c>
@@ -11303,7 +11306,7 @@
         <v>-4.8652182622342E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="17">
+    <row r="138" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A138" s="12" t="s">
         <v>573</v>
       </c>
@@ -11362,7 +11365,7 @@
         <v>6.4769795780332037E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="17">
+    <row r="139" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A139" s="12" t="s">
         <v>576</v>
       </c>
@@ -11421,7 +11424,7 @@
         <v>-3.4374973382235038E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="17">
+    <row r="140" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A140" s="12" t="s">
         <v>579</v>
       </c>
@@ -11480,7 +11483,7 @@
         <v>-2.0950939342629107E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="17">
+    <row r="141" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A141" s="12" t="s">
         <v>580</v>
       </c>
@@ -11539,7 +11542,7 @@
         <v>-3.0339725635474154E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="17">
+    <row r="142" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A142" s="12" t="s">
         <v>582</v>
       </c>
@@ -11598,7 +11601,7 @@
         <v>-2.3993298941104857E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="17">
+    <row r="143" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A143" s="12" t="s">
         <v>409</v>
       </c>
@@ -11657,7 +11660,7 @@
         <v>-3.5408975296677327E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="17">
+    <row r="144" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A144" s="12" t="s">
         <v>414</v>
       </c>
@@ -11716,7 +11719,7 @@
         <v>5.5951582517539608E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="17">
+    <row r="145" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A145" s="12" t="s">
         <v>417</v>
       </c>
@@ -11775,7 +11778,7 @@
         <v>-4.7208187889274715E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="17">
+    <row r="146" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A146" s="12" t="s">
         <v>421</v>
       </c>
@@ -11834,7 +11837,7 @@
         <v>3.1196820132286404E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="17">
+    <row r="147" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A147" s="12" t="s">
         <v>425</v>
       </c>
@@ -11893,7 +11896,7 @@
         <v>-2.7973394033711085E-3</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="17">
+    <row r="148" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A148" s="12" t="s">
         <v>427</v>
       </c>
@@ -11952,7 +11955,7 @@
         <v>2.6871385420357302E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="17">
+    <row r="149" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A149" s="12" t="s">
         <v>429</v>
       </c>
@@ -12011,7 +12014,7 @@
         <v>1.2261865689088372E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="17">
+    <row r="150" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A150" s="12" t="s">
         <v>434</v>
       </c>
@@ -12070,7 +12073,7 @@
         <v>-1.5825242373925567E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="17">
+    <row r="151" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A151" s="12" t="s">
         <v>438</v>
       </c>
@@ -12129,7 +12132,7 @@
         <v>-1.6008169924145593E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="17">
+    <row r="152" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A152" s="12" t="s">
         <v>441</v>
       </c>
@@ -12188,7 +12191,7 @@
         <v>-4.7181978106071609E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="17">
+    <row r="153" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A153" s="12" t="s">
         <v>444</v>
       </c>
@@ -12247,7 +12250,7 @@
         <v>8.020403369240578E-3</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="17">
+    <row r="154" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A154" s="12" t="s">
         <v>446</v>
       </c>
@@ -12306,7 +12309,7 @@
         <v>-6.3934997308142984E-3</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="17">
+    <row r="155" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A155" s="12" t="s">
         <v>448</v>
       </c>
@@ -12365,7 +12368,7 @@
         <v>-1.1746288023388132E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="17">
+    <row r="156" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A156" s="12" t="s">
         <v>451</v>
       </c>
@@ -12424,7 +12427,7 @@
         <v>2.1346158330944821E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="17">
+    <row r="157" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A157" s="12" t="s">
         <v>454</v>
       </c>
@@ -12483,7 +12486,7 @@
         <v>1.0819653216385299E-3</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="17">
+    <row r="158" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A158" s="12" t="s">
         <v>459</v>
       </c>
@@ -12542,7 +12545,7 @@
         <v>2.3249250133680902E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="17">
+    <row r="159" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A159" s="12" t="s">
         <v>463</v>
       </c>
@@ -12601,7 +12604,7 @@
         <v>8.5491483442413613E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="17">
+    <row r="160" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A160" s="12" t="s">
         <v>466</v>
       </c>
@@ -12660,7 +12663,7 @@
         <v>-4.2281954839773761E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="17">
+    <row r="161" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A161" s="12" t="s">
         <v>468</v>
       </c>
@@ -12719,7 +12722,7 @@
         <v>3.8352173125134892E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="17">
+    <row r="162" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A162" s="12" t="s">
         <v>471</v>
       </c>
@@ -12778,7 +12781,7 @@
         <v>-8.7335740711981958E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="17">
+    <row r="163" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A163" s="12" t="s">
         <v>473</v>
       </c>
@@ -12837,7 +12840,7 @@
         <v>-3.6123833220147894E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="17">
+    <row r="164" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A164" s="12" t="s">
         <v>475</v>
       </c>
@@ -12896,7 +12899,7 @@
         <v>-4.1604963959154168E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="17">
+    <row r="165" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A165" s="12" t="s">
         <v>478</v>
       </c>
@@ -12955,7 +12958,7 @@
         <v>-8.9782986281662883E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="17">
+    <row r="166" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A166" s="12" t="s">
         <v>482</v>
       </c>
@@ -13014,7 +13017,7 @@
         <v>-0.12261598173535156</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="17">
+    <row r="167" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A167" s="12" t="s">
         <v>486</v>
       </c>
@@ -13073,7 +13076,7 @@
         <v>-0.11050366861857248</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="17">
+    <row r="168" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A168" s="12" t="s">
         <v>487</v>
       </c>
@@ -13132,7 +13135,7 @@
         <v>-8.3915213036268643E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="17">
+    <row r="169" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A169" s="12" t="s">
         <v>492</v>
       </c>
@@ -13191,7 +13194,7 @@
         <v>-5.1904278927215192E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="17">
+    <row r="170" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A170" s="12" t="s">
         <v>494</v>
       </c>
@@ -13250,7 +13253,7 @@
         <v>-3.3721013461863236E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="17">
+    <row r="171" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A171" s="12" t="s">
         <v>497</v>
       </c>
@@ -13309,7 +13312,7 @@
         <v>-2.0843493411355024E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="17">
+    <row r="172" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A172" s="12" t="s">
         <v>500</v>
       </c>
@@ -13368,7 +13371,7 @@
         <v>2.6020437340701212E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="17">
+    <row r="173" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A173" s="12" t="s">
         <v>297</v>
       </c>
@@ -13427,7 +13430,7 @@
         <v>-5.1533205595115797E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="17">
+    <row r="174" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A174" s="12" t="s">
         <v>302</v>
       </c>
@@ -13486,7 +13489,7 @@
         <v>8.2148538018878936E-4</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="17">
+    <row r="175" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A175" s="12" t="s">
         <v>307</v>
       </c>
@@ -13545,7 +13548,7 @@
         <v>-5.2560848498338399E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="17">
+    <row r="176" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A176" s="12" t="s">
         <v>311</v>
       </c>
@@ -13604,7 +13607,7 @@
         <v>-5.270496689749863E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="17">
+    <row r="177" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A177" s="12" t="s">
         <v>314</v>
       </c>
@@ -13663,7 +13666,7 @@
         <v>-4.5429118838586954E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="17">
+    <row r="178" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A178" s="12" t="s">
         <v>318</v>
       </c>
@@ -13722,7 +13725,7 @@
         <v>-2.0828984735350845E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="17">
+    <row r="179" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A179" s="12" t="s">
         <v>321</v>
       </c>
@@ -13781,7 +13784,7 @@
         <v>-3.7755020441898428E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="17">
+    <row r="180" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A180" s="12" t="s">
         <v>326</v>
       </c>
@@ -13840,7 +13843,7 @@
         <v>9.2352676866176413E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="17">
+    <row r="181" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A181" s="12" t="s">
         <v>332</v>
       </c>
@@ -13899,7 +13902,7 @@
         <v>1.6430458473561366E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="17">
+    <row r="182" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A182" s="12" t="s">
         <v>335</v>
       </c>
@@ -13958,7 +13961,7 @@
         <v>-6.4859880841561204E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="17">
+    <row r="183" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A183" s="12" t="s">
         <v>338</v>
       </c>
@@ -14017,7 +14020,7 @@
         <v>-8.8027231725488944E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="17">
+    <row r="184" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A184" s="12" t="s">
         <v>343</v>
       </c>
@@ -14076,7 +14079,7 @@
         <v>3.9292317421567663E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="17">
+    <row r="185" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A185" s="12" t="s">
         <v>348</v>
       </c>
@@ -14135,7 +14138,7 @@
         <v>-1.1024978313943098E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="17">
+    <row r="186" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A186" s="12" t="s">
         <v>351</v>
       </c>
@@ -14194,7 +14197,7 @@
         <v>-3.5315712290992778E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="17">
+    <row r="187" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A187" s="12" t="s">
         <v>355</v>
       </c>
@@ -14253,7 +14256,7 @@
         <v>-8.1654439121027683E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="17">
+    <row r="188" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A188" s="12" t="s">
         <v>359</v>
       </c>
@@ -14312,7 +14315,7 @@
         <v>-0.12807063681173217</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="17">
+    <row r="189" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A189" s="12" t="s">
         <v>361</v>
       </c>
@@ -14371,7 +14374,7 @@
         <v>-7.7062196890682236E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="17">
+    <row r="190" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A190" s="12" t="s">
         <v>363</v>
       </c>
@@ -14430,7 +14433,7 @@
         <v>-2.9621787538812429E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="17">
+    <row r="191" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A191" s="12" t="s">
         <v>367</v>
       </c>
@@ -14489,7 +14492,7 @@
         <v>-3.8781717687504137E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="17">
+    <row r="192" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A192" s="12" t="s">
         <v>369</v>
       </c>
@@ -14548,7 +14551,7 @@
         <v>-8.8599722327506961E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="17">
+    <row r="193" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A193" s="12" t="s">
         <v>373</v>
       </c>
@@ -14607,7 +14610,7 @@
         <v>-1.843244366110721E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="17">
+    <row r="194" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A194" s="12" t="s">
         <v>379</v>
       </c>
@@ -14666,7 +14669,7 @@
         <v>1.0267007066223494E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="17">
+    <row r="195" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A195" s="12" t="s">
         <v>381</v>
       </c>
@@ -14725,7 +14728,7 @@
         <v>4.2892609639004028E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="17">
+    <row r="196" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A196" s="12" t="s">
         <v>383</v>
       </c>
@@ -14784,7 +14787,7 @@
         <v>8.9072107134379547E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="17">
+    <row r="197" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A197" s="12" t="s">
         <v>386</v>
       </c>
@@ -14843,7 +14846,7 @@
         <v>7.6752775092991249E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="17">
+    <row r="198" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A198" s="12" t="s">
         <v>390</v>
       </c>
@@ -14902,7 +14905,7 @@
         <v>-4.055181473337819E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="17">
+    <row r="199" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A199" s="12" t="s">
         <v>393</v>
       </c>
@@ -14961,7 +14964,7 @@
         <v>-1.8743378697742646E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="17">
+    <row r="200" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A200" s="12" t="s">
         <v>396</v>
       </c>
@@ -15020,7 +15023,7 @@
         <v>-2.8442781428962257E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="17">
+    <row r="201" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A201" s="12" t="s">
         <v>400</v>
       </c>
@@ -15079,7 +15082,7 @@
         <v>1.2338624475800964E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="17">
+    <row r="202" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A202" s="12" t="s">
         <v>403</v>
       </c>
@@ -15138,7 +15141,7 @@
         <v>2.0374500961494795E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="17">
+    <row r="203" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A203" s="12" t="s">
         <v>405</v>
       </c>
@@ -15197,7 +15200,7 @@
         <v>-1.7117410081996513E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="17">
+    <row r="204" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A204" s="12" t="s">
         <v>177</v>
       </c>
@@ -15256,7 +15259,7 @@
         <v>2.1898308570141582E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="17">
+    <row r="205" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A205" s="12" t="s">
         <v>181</v>
       </c>
@@ -15315,7 +15318,7 @@
         <v>5.5929665962880667E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="17">
+    <row r="206" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A206" s="12" t="s">
         <v>183</v>
       </c>
@@ -15374,7 +15377,7 @@
         <v>1.4295908731586831E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="17">
+    <row r="207" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A207" s="12" t="s">
         <v>188</v>
       </c>
@@ -15433,7 +15436,7 @@
         <v>8.7420616224683769E-4</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="17">
+    <row r="208" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A208" s="12" t="s">
         <v>194</v>
       </c>
@@ -15492,7 +15495,7 @@
         <v>-2.6887062811518321E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="17">
+    <row r="209" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A209" s="12" t="s">
         <v>198</v>
       </c>
@@ -15551,7 +15554,7 @@
         <v>1.746969319904812E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="17">
+    <row r="210" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A210" s="12" t="s">
         <v>202</v>
       </c>
@@ -15610,7 +15613,7 @@
         <v>2.2032714662974223E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="17">
+    <row r="211" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A211" s="12" t="s">
         <v>207</v>
       </c>
@@ -15669,7 +15672,7 @@
         <v>-1.5205505231359249E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="17">
+    <row r="212" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A212" s="12" t="s">
         <v>212</v>
       </c>
@@ -15728,7 +15731,7 @@
         <v>-4.231255133197085E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="17">
+    <row r="213" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A213" s="12" t="s">
         <v>215</v>
       </c>
@@ -15787,7 +15790,7 @@
         <v>-7.6475028255852005E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="17">
+    <row r="214" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A214" s="12" t="s">
         <v>221</v>
       </c>
@@ -15846,7 +15849,7 @@
         <v>1.2331251247350865E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="17">
+    <row r="215" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A215" s="12" t="s">
         <v>226</v>
       </c>
@@ -15905,7 +15908,7 @@
         <v>2.5099738635953914E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="17">
+    <row r="216" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A216" s="12" t="s">
         <v>230</v>
       </c>
@@ -15964,7 +15967,7 @@
         <v>-6.3470952277877067E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="17">
+    <row r="217" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A217" s="12" t="s">
         <v>233</v>
       </c>
@@ -16023,7 +16026,7 @@
         <v>-3.0551322497656359E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="17">
+    <row r="218" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A218" s="12" t="s">
         <v>237</v>
       </c>
@@ -16082,7 +16085,7 @@
         <v>-2.3942235909677929E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="17">
+    <row r="219" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A219" s="12" t="s">
         <v>239</v>
       </c>
@@ -16141,7 +16144,7 @@
         <v>-7.899054077155393E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="17">
+    <row r="220" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A220" s="12" t="s">
         <v>244</v>
       </c>
@@ -16200,7 +16203,7 @@
         <v>-2.556252748424746E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="17">
+    <row r="221" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A221" s="12" t="s">
         <v>249</v>
       </c>
@@ -16259,7 +16262,7 @@
         <v>-1.4126678043581387E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="17">
+    <row r="222" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A222" s="12" t="s">
         <v>254</v>
       </c>
@@ -16318,7 +16321,7 @@
         <v>1.4756414035037272E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="17">
+    <row r="223" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A223" s="12" t="s">
         <v>260</v>
       </c>
@@ -16377,7 +16380,7 @@
         <v>-1.7681544504539268E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="17">
+    <row r="224" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A224" s="12" t="s">
         <v>263</v>
       </c>
@@ -16436,7 +16439,7 @@
         <v>2.029345548134415E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="17">
+    <row r="225" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A225" s="12" t="s">
         <v>264</v>
       </c>
@@ -16495,7 +16498,7 @@
         <v>2.0212906773948967E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="17">
+    <row r="226" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A226" s="12" t="s">
         <v>268</v>
       </c>
@@ -16554,7 +16557,7 @@
         <v>7.4876282227176669E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="17">
+    <row r="227" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A227" s="12" t="s">
         <v>271</v>
       </c>
@@ -16613,7 +16616,7 @@
         <v>1.4788564547085315E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="17">
+    <row r="228" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A228" s="12" t="s">
         <v>273</v>
       </c>
@@ -16672,7 +16675,7 @@
         <v>1.1203676591368438E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="17">
+    <row r="229" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A229" s="12" t="s">
         <v>276</v>
       </c>
@@ -16731,7 +16734,7 @@
         <v>-3.0402559981217089E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="17">
+    <row r="230" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A230" s="12" t="s">
         <v>282</v>
       </c>
@@ -16790,7 +16793,7 @@
         <v>3.6652103340181257E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="17">
+    <row r="231" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A231" s="12" t="s">
         <v>287</v>
       </c>
@@ -16849,7 +16852,7 @@
         <v>4.3639949722986855E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="17">
+    <row r="232" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A232" s="12" t="s">
         <v>290</v>
       </c>
@@ -16908,7 +16911,7 @@
         <v>2.2299037769906219E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="17">
+    <row r="233" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A233" s="12" t="s">
         <v>292</v>
       </c>
@@ -16967,7 +16970,7 @@
         <v>-8.9244779472520738E-3</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="17">
+    <row r="234" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A234" s="12" t="s">
         <v>295</v>
       </c>
@@ -17026,7 +17029,7 @@
         <v>-4.9064909346456374E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="17">
+    <row r="235" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A235" s="6" t="s">
         <v>22</v>
       </c>
@@ -17085,7 +17088,7 @@
         <v>-0.16819661498566574</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="17">
+    <row r="236" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A236" s="6" t="s">
         <v>29</v>
       </c>
@@ -17144,7 +17147,7 @@
         <v>-0.3261578629576225</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="17">
+    <row r="237" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A237" s="6" t="s">
         <v>34</v>
       </c>
@@ -17203,7 +17206,7 @@
         <v>-0.31697739628532928</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="17">
+    <row r="238" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A238" s="6" t="s">
         <v>40</v>
       </c>
@@ -17262,7 +17265,7 @@
         <v>-0.15826603314950347</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="17">
+    <row r="239" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A239" s="6" t="s">
         <v>47</v>
       </c>
@@ -17321,7 +17324,7 @@
         <v>-2.9594273216998208E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="17">
+    <row r="240" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A240" s="6" t="s">
         <v>54</v>
       </c>
@@ -17380,7 +17383,7 @@
         <v>2.0432153402609832E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="17">
+    <row r="241" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A241" s="6" t="s">
         <v>60</v>
       </c>
@@ -17439,7 +17442,7 @@
         <v>6.6021897454396558E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="17">
+    <row r="242" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A242" s="6" t="s">
         <v>66</v>
       </c>
@@ -17498,7 +17501,7 @@
         <v>0.20775660900956486</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="17">
+    <row r="243" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A243" s="6" t="s">
         <v>72</v>
       </c>
@@ -17557,7 +17560,7 @@
         <v>0.42818386102577943</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="17">
+    <row r="244" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A244" s="6" t="s">
         <v>77</v>
       </c>
@@ -17616,7 +17619,7 @@
         <v>0.38479343771754698</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="17">
+    <row r="245" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A245" s="6" t="s">
         <v>83</v>
       </c>
@@ -17675,7 +17678,7 @@
         <v>0.14750125931554814</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="17">
+    <row r="246" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A246" s="6" t="s">
         <v>88</v>
       </c>
@@ -17734,7 +17737,7 @@
         <v>1.6397425661629147E-3</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="17">
+    <row r="247" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A247" s="6" t="s">
         <v>94</v>
       </c>
@@ -17793,7 +17796,7 @@
         <v>-1.2213029660052272E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="17">
+    <row r="248" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A248" s="6" t="s">
         <v>101</v>
       </c>
@@ -17852,7 +17855,7 @@
         <v>0.20224472475050484</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="17">
+    <row r="249" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A249" s="6" t="s">
         <v>104</v>
       </c>
@@ -17911,7 +17914,7 @@
         <v>6.5632249900405407E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="17">
+    <row r="250" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A250" s="6" t="s">
         <v>110</v>
       </c>
@@ -17970,7 +17973,7 @@
         <v>5.0103141085291493E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="17">
+    <row r="251" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A251" s="6" t="s">
         <v>113</v>
       </c>
@@ -18029,7 +18032,7 @@
         <v>8.5699692990361717E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="17">
+    <row r="252" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A252" s="6" t="s">
         <v>118</v>
       </c>
@@ -18088,7 +18091,7 @@
         <v>5.3801736050552072E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="17">
+    <row r="253" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A253" s="6" t="s">
         <v>124</v>
       </c>
@@ -18147,7 +18150,7 @@
         <v>9.735729690084366E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="17">
+    <row r="254" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A254" s="6" t="s">
         <v>129</v>
       </c>
@@ -18206,7 +18209,7 @@
         <v>6.5572641712733609E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="17">
+    <row r="255" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A255" s="6" t="s">
         <v>133</v>
       </c>
@@ -18265,7 +18268,7 @@
         <v>-0.13655736640741326</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="17">
+    <row r="256" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A256" s="6" t="s">
         <v>137</v>
       </c>
@@ -18324,7 +18327,7 @@
         <v>-3.9980780109832657E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="17">
+    <row r="257" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A257" s="6" t="s">
         <v>143</v>
       </c>
@@ -18383,7 +18386,7 @@
         <v>2.6075281310838794E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="17">
+    <row r="258" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A258" s="6" t="s">
         <v>149</v>
       </c>
@@ -18442,7 +18445,7 @@
         <v>-4.7563472851373583E-3</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="17">
+    <row r="259" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A259" s="6" t="s">
         <v>154</v>
       </c>
@@ -18501,7 +18504,7 @@
         <v>-8.787834884544609E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="17">
+    <row r="260" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A260" s="6" t="s">
         <v>159</v>
       </c>
@@ -18560,7 +18563,7 @@
         <v>-4.2647148144349709E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="17">
+    <row r="261" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A261" s="6" t="s">
         <v>163</v>
       </c>
@@ -18619,7 +18622,7 @@
         <v>-2.8484786709496814E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="17">
+    <row r="262" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A262" s="6" t="s">
         <v>167</v>
       </c>
@@ -18678,7 +18681,7 @@
         <v>-3.1042847493465683E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="17">
+    <row r="263" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A263" s="6" t="s">
         <v>172</v>
       </c>
@@ -18737,7 +18740,7 @@
         <v>1.9527827440434398E-4</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="22" customHeight="1">
+    <row r="264" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="12" t="s">
         <v>816</v>
       </c>
@@ -18796,7 +18799,7 @@
         <v>1.810047892161106E-3</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="22" customHeight="1">
+    <row r="265" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="12" t="s">
         <v>821</v>
       </c>
@@ -18855,7 +18858,7 @@
         <v>-4.9799229636680001E-2</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="22" customHeight="1">
+    <row r="266" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="12" t="s">
         <v>822</v>
       </c>
@@ -18914,7 +18917,7 @@
         <v>-3.0479227547543598E-2</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="22" customHeight="1">
+    <row r="267" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="12" t="s">
         <v>823</v>
       </c>
@@ -18973,7 +18976,7 @@
         <v>-4.0986031950742602E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="22" customHeight="1">
+    <row r="268" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="12" t="s">
         <v>824</v>
       </c>
@@ -19032,7 +19035,7 @@
         <v>-1.1870471763171648E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="22" customHeight="1">
+    <row r="269" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="12" t="s">
         <v>825</v>
       </c>
@@ -19091,7 +19094,7 @@
         <v>3.6543052122267228E-3</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="22" customHeight="1">
+    <row r="270" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="12" t="s">
         <v>828</v>
       </c>
@@ -19150,12 +19153,12 @@
         <v>-2.9698259499921845E-3</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="22" customHeight="1">
+    <row r="271" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="12" t="s">
         <v>829</v>
       </c>
       <c r="B271" s="13">
-        <v>208252176183</v>
+        <v>408252176183</v>
       </c>
       <c r="C271" s="13">
         <v>211001407747</v>
@@ -19198,7 +19201,7 @@
       </c>
       <c r="P271" s="20">
         <f t="shared" si="14"/>
-        <v>-4.0393204091784894E-2</v>
+        <v>0.88118832604787423</v>
       </c>
       <c r="Q271" s="20">
         <f t="shared" si="15"/>

--- a/Cursor/3_쿠팡 모니터링/cp_payment.xlsx
+++ b/Cursor/3_쿠팡 모니터링/cp_payment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\hana\Cursor\3_쿠팡 모니터링\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{331BE418-4C4F-4B4A-9B35-94BEDA8862CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D481030A-5E0C-4180-8356-26AF89DC2B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Cursor/3_쿠팡 모니터링/cp_payment.xlsx
+++ b/Cursor/3_쿠팡 모니터링/cp_payment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\hana\Cursor\3_쿠팡 모니터링\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D481030A-5E0C-4180-8356-26AF89DC2B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF1B2B2-7CF7-42A3-842D-25043F2347EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19158,7 +19158,7 @@
         <v>829</v>
       </c>
       <c r="B271" s="13">
-        <v>408252176183</v>
+        <v>208252176183</v>
       </c>
       <c r="C271" s="13">
         <v>211001407747</v>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="P271" s="20">
         <f t="shared" si="14"/>
-        <v>0.88118832604787423</v>
+        <v>-4.0393204091784894E-2</v>
       </c>
       <c r="Q271" s="20">
         <f t="shared" si="15"/>
